--- a/exports/trend_1d/NYKAA_full_report.xlsx
+++ b/exports/trend_1d/NYKAA_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q27"/>
+  <dimension ref="A1:U27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>22.18</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44547</v>
+        <v>44550</v>
       </c>
       <c r="H2" t="n">
-        <v>349.8</v>
+        <v>325.45</v>
       </c>
       <c r="I2" t="n">
         <v>334.53452565</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K2" t="n">
-        <v>-12.46</v>
+        <v>-18.56</v>
       </c>
       <c r="L2" t="n">
-        <v>17.42</v>
+        <v>20.33</v>
       </c>
       <c r="M2" t="n">
         <v>4.87</v>
       </c>
       <c r="N2" t="n">
-        <v>5.74</v>
+        <v>6.96</v>
       </c>
       <c r="O2" t="n">
         <v>6.67</v>
@@ -564,7 +587,19 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>23.79</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44643</v>
+        <v>44644</v>
       </c>
       <c r="H3" t="n">
-        <v>256.55</v>
+        <v>263.8</v>
       </c>
       <c r="I3" t="n">
         <v>260.8786438808841</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K3" t="n">
-        <v>21.17</v>
+        <v>18.94</v>
       </c>
       <c r="L3" t="n">
         <v>11.65</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>4</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>14.84</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44673</v>
+        <v>44676</v>
       </c>
       <c r="H4" t="n">
-        <v>303.85</v>
+        <v>281.15</v>
       </c>
       <c r="I4" t="n">
         <v>281.5477889092852</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K4" t="n">
-        <v>15.18</v>
+        <v>6.58</v>
       </c>
       <c r="L4" t="n">
         <v>2.75</v>
@@ -669,7 +716,7 @@
         <v>1.12</v>
       </c>
       <c r="N4" t="n">
-        <v>4.83</v>
+        <v>7.47</v>
       </c>
       <c r="O4" t="n">
         <v>2.83</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>17.19</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44865</v>
+        <v>44866</v>
       </c>
       <c r="H5" t="n">
-        <v>192.1</v>
+        <v>197.55</v>
       </c>
       <c r="I5" t="n">
         <v>193.0816079068578</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K5" t="n">
-        <v>31.67</v>
+        <v>29.74</v>
       </c>
       <c r="L5" t="n">
         <v>7.9</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>130</v>
+        <v>131</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>8</v>
+      </c>
+      <c r="U5" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>15.11</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44911</v>
+        <v>44914</v>
       </c>
       <c r="H6" t="n">
-        <v>168.05</v>
+        <v>163.25</v>
       </c>
       <c r="I6" t="n">
         <v>167.6906475954452</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K6" t="n">
-        <v>-14.93</v>
+        <v>-17.36</v>
       </c>
       <c r="L6" t="n">
-        <v>16.15</v>
+        <v>19.16</v>
       </c>
       <c r="M6" t="n">
         <v>5.49</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>12.37</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44964</v>
+        <v>44965</v>
       </c>
       <c r="H7" t="n">
-        <v>139.1</v>
+        <v>146.3</v>
       </c>
       <c r="I7" t="n">
         <v>144.9105212768727</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K7" t="n">
-        <v>14.79</v>
+        <v>10.38</v>
       </c>
       <c r="L7" t="n">
         <v>3.64</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>16.45</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>45012</v>
+        <v>45013</v>
       </c>
       <c r="H8" t="n">
-        <v>133.75</v>
+        <v>127.75</v>
       </c>
       <c r="I8" t="n">
         <v>130.5705219700382</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K8" t="n">
-        <v>-8.58</v>
+        <v>-12.68</v>
       </c>
       <c r="L8" t="n">
-        <v>9.98</v>
+        <v>13.74</v>
       </c>
       <c r="M8" t="n">
         <v>5.39</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>15.28</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>45050</v>
+        <v>45051</v>
       </c>
       <c r="H9" t="n">
-        <v>128.6</v>
+        <v>129.85</v>
       </c>
       <c r="I9" t="n">
         <v>129.812407845168</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.67</v>
+        <v>-1.64</v>
       </c>
       <c r="L9" t="n">
         <v>8.65</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,28 +1109,28 @@
         <v>11.22</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>45149</v>
+        <v>45152</v>
       </c>
       <c r="H10" t="n">
-        <v>146.2</v>
+        <v>134.3</v>
       </c>
       <c r="I10" t="n">
         <v>136.3903248785067</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="K10" t="n">
-        <v>12.59</v>
+        <v>3.43</v>
       </c>
       <c r="L10" t="n">
         <v>5.93</v>
       </c>
       <c r="M10" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="N10" t="n">
-        <v>2.65</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="O10" t="n">
         <v>0.97</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>13.25</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>45176</v>
+        <v>45177</v>
       </c>
       <c r="H11" t="n">
-        <v>144.35</v>
+        <v>146.05</v>
       </c>
       <c r="I11" t="n">
         <v>145.5307643353788</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K11" t="n">
-        <v>-7.48</v>
+        <v>-8.75</v>
       </c>
       <c r="L11" t="n">
-        <v>8.19</v>
+        <v>10.13</v>
       </c>
       <c r="M11" t="n">
         <v>1.62</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,28 +1247,28 @@
         <v>8.16</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>45219</v>
+        <v>45222</v>
       </c>
       <c r="H12" t="n">
-        <v>143.95</v>
+        <v>139.05</v>
       </c>
       <c r="I12" t="n">
         <v>139.4031899715806</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.44</v>
+        <v>-4.79</v>
       </c>
       <c r="L12" t="n">
-        <v>3.66</v>
+        <v>5.96</v>
       </c>
       <c r="M12" t="n">
         <v>2.42</v>
       </c>
       <c r="N12" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="O12" t="n">
         <v>1.18</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>10.48</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>45242</v>
+        <v>45243</v>
       </c>
       <c r="H13" t="n">
-        <v>148.6</v>
+        <v>151.55</v>
       </c>
       <c r="I13" t="n">
         <v>151.1907196103008</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K13" t="n">
-        <v>-6.87</v>
+        <v>-8.99</v>
       </c>
       <c r="L13" t="n">
         <v>11.33</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>9.15</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>45307</v>
+        <v>45308</v>
       </c>
       <c r="H14" t="n">
-        <v>173.1</v>
+        <v>168.4</v>
       </c>
       <c r="I14" t="n">
         <v>171.1745904685369</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K14" t="n">
-        <v>14.22</v>
+        <v>11.12</v>
       </c>
       <c r="L14" t="n">
         <v>1.98</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>14.78</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="H15" t="n">
-        <v>164.55</v>
+        <v>168.45</v>
       </c>
       <c r="I15" t="n">
         <v>165.1421477415508</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K15" t="n">
-        <v>2.29</v>
+        <v>-0.03</v>
       </c>
       <c r="L15" t="n">
         <v>3.44</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>4</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>10.53</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45440</v>
+        <v>45441</v>
       </c>
       <c r="H16" t="n">
-        <v>166.05</v>
+        <v>161.75</v>
       </c>
       <c r="I16" t="n">
         <v>163.1030573927721</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.42</v>
+        <v>-3.98</v>
       </c>
       <c r="L16" t="n">
         <v>4.51</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>11.89</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45469</v>
+        <v>45470</v>
       </c>
       <c r="H17" t="n">
-        <v>174.68</v>
+        <v>176.65</v>
       </c>
       <c r="I17" t="n">
         <v>176.5705287608972</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K17" t="n">
-        <v>-7.99</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="L17" t="n">
         <v>10.69</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>10.67</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45579</v>
+        <v>45580</v>
       </c>
       <c r="H18" t="n">
-        <v>192.41</v>
+        <v>188.68</v>
       </c>
       <c r="I18" t="n">
         <v>191.032386944223</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K18" t="n">
-        <v>8.92</v>
+        <v>6.81</v>
       </c>
       <c r="L18" t="n">
         <v>3.48</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>11.17</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45689</v>
+        <v>45691</v>
       </c>
       <c r="H19" t="n">
-        <v>175.53</v>
+        <v>178.9</v>
       </c>
       <c r="I19" t="n">
         <v>176.9692166814644</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="K19" t="n">
-        <v>6.97</v>
+        <v>5.18</v>
       </c>
       <c r="L19" t="n">
         <v>3.76</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>5</v>
+      </c>
+      <c r="U19" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>12</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="H20" t="n">
-        <v>252.95</v>
+        <v>247.05</v>
       </c>
       <c r="I20" t="n">
         <v>248.7025197981048</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K20" t="n">
-        <v>41.39</v>
+        <v>38.09</v>
       </c>
       <c r="L20" t="n">
         <v>13.42</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>210</v>
+        <v>211</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>11</v>
+      </c>
+      <c r="U20" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>10.19</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="H21" t="n">
-        <v>263.55</v>
+        <v>265.15</v>
       </c>
       <c r="I21" t="n">
         <v>263.756890682088</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K21" t="n">
-        <v>-6.68</v>
+        <v>-7.33</v>
       </c>
       <c r="L21" t="n">
         <v>8.16</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>7.36</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>46038</v>
+        <v>46041</v>
       </c>
       <c r="H22" t="n">
-        <v>252.85</v>
+        <v>250.8</v>
       </c>
       <c r="I22" t="n">
         <v>251.561499359019</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K22" t="n">
-        <v>-4.64</v>
+        <v>-5.41</v>
       </c>
       <c r="L22" t="n">
         <v>6.32</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>8.539999999999999</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="H23" t="n">
-        <v>251.03</v>
+        <v>258.29</v>
       </c>
       <c r="I23" t="n">
         <v>255.8209968312993</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.09</v>
+        <v>-2.99</v>
       </c>
       <c r="L23" t="n">
-        <v>2.33</v>
+        <v>4.96</v>
       </c>
       <c r="M23" t="n">
         <v>1.84</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>9.6</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="H24" t="n">
-        <v>254.8</v>
+        <v>249.7</v>
       </c>
       <c r="I24" t="n">
         <v>253.0152156970556</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.35</v>
+        <v>-3.33</v>
       </c>
       <c r="L24" t="n">
-        <v>3.21</v>
+        <v>5.53</v>
       </c>
       <c r="M24" t="n">
         <v>3.12</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>9.19</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="H25" t="n">
-        <v>254.93</v>
+        <v>259.49</v>
       </c>
       <c r="I25" t="n">
         <v>259.1307358064387</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.09</v>
+        <v>-3.92</v>
       </c>
       <c r="L25" t="n">
-        <v>3.88</v>
+        <v>4.3</v>
       </c>
       <c r="M25" t="n">
         <v>3.25</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>10.2</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="H26" t="n">
-        <v>321.9</v>
+        <v>319.3</v>
       </c>
       <c r="I26" t="n">
         <v>319.5816415479135</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K26" t="n">
-        <v>24.05</v>
+        <v>23.05</v>
       </c>
       <c r="L26" t="n">
         <v>3.13</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>133</v>
+        <v>134</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>7</v>
+      </c>
+      <c r="U26" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="27">
@@ -1983,6 +2306,14 @@
       <c r="Q27" t="n">
         <v>4</v>
       </c>
+      <c r="R27" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4153,7 +4484,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>70.09999999999999</v>
+        <v>71.7</v>
       </c>
     </row>
     <row r="6">
@@ -4163,7 +4494,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7">
@@ -4173,7 +4504,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="8">
@@ -4183,7 +4514,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
@@ -4193,7 +4524,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10">
@@ -4203,7 +4534,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>157</v>
+        <v>158.4</v>
       </c>
     </row>
     <row r="11">
@@ -4213,7 +4544,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -4223,7 +4554,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13">
@@ -4233,7 +4564,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14">
@@ -4243,7 +4574,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.66</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="15">
@@ -4253,7 +4584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.5</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="16">
@@ -4263,7 +4594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.75</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="17">
@@ -4273,7 +4604,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>41.39</v>
+        <v>38.09</v>
       </c>
     </row>
     <row r="18">
@@ -4283,7 +4614,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -4293,7 +4624,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7.02</v>
+        <v>7.79</v>
       </c>
     </row>
     <row r="20">
@@ -4303,7 +4634,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.93</v>
+        <v>5.96</v>
       </c>
     </row>
     <row r="21">
@@ -4313,7 +4644,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>17.42</v>
+        <v>20.33</v>
       </c>
     </row>
     <row r="22">
@@ -4323,7 +4654,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23">
@@ -4333,7 +4664,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -4363,7 +4694,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.23</v>
+        <v>5.62</v>
       </c>
     </row>
     <row r="27">
@@ -4383,7 +4714,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29">
